--- a/AAII_Financials/Quarterly/TURB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TURB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="92">
   <si>
     <t>TURB</t>
   </si>
@@ -831,10 +831,10 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="E10" s="3">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="F10" s="3">
         <v>700</v>
@@ -1101,10 +1101,10 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>8300</v>
+        <v>8200</v>
       </c>
       <c r="E17" s="3">
-        <v>8300</v>
+        <v>8200</v>
       </c>
       <c r="F17" s="3">
         <v>3900</v>
@@ -2103,10 +2103,10 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F42" s="3">
         <v>300</v>
@@ -2150,10 +2150,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>14300</v>
+        <v>14000</v>
       </c>
       <c r="E43" s="3">
-        <v>14300</v>
+        <v>14000</v>
       </c>
       <c r="F43" s="3">
         <v>1600</v>
@@ -2197,10 +2197,10 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="E44" s="3">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="F44" s="3">
         <v>4600</v>
@@ -2243,11 +2243,11 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>8</v>
+      <c r="D45" s="3">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3">
+        <v>0</v>
       </c>
       <c r="F45" s="3">
         <v>0</v>
@@ -2752,10 +2752,10 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>14800</v>
+        <v>14400</v>
       </c>
       <c r="E57" s="3">
-        <v>14800</v>
+        <v>14400</v>
       </c>
       <c r="F57" s="3">
         <v>2200</v>
@@ -2799,10 +2799,10 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>5600</v>
+        <v>6800</v>
       </c>
       <c r="E58" s="3">
-        <v>5600</v>
+        <v>6800</v>
       </c>
       <c r="F58" s="3">
         <v>6800</v>
@@ -2846,10 +2846,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3400</v>
+        <v>2500</v>
       </c>
       <c r="E59" s="3">
-        <v>3400</v>
+        <v>2500</v>
       </c>
       <c r="F59" s="3">
         <v>100</v>
@@ -3429,10 +3429,10 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-7600</v>
+        <v>-6000</v>
       </c>
       <c r="E72" s="3">
-        <v>-7600</v>
+        <v>-6000</v>
       </c>
       <c r="F72" s="3">
         <v>-6300</v>
